--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/服务交付界面表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/服务交付界面表.xlsx
@@ -459,7 +459,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -482,7 +486,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -505,7 +513,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -528,7 +540,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -551,7 +567,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -574,7 +594,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -597,7 +621,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -620,7 +648,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -643,7 +675,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -666,7 +702,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -689,7 +729,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -712,7 +756,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -735,7 +783,11 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1655,11 +1707,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1682,11 +1730,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1709,11 +1753,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1736,11 +1776,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1763,11 +1799,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1790,11 +1822,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1817,11 +1845,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1844,11 +1868,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1871,11 +1891,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1898,11 +1914,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1925,11 +1937,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1952,11 +1960,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -1979,11 +1983,7 @@
           <t>华为</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
